--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,12 +200,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -526,7 +544,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -550,16 +568,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -568,90 +586,99 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -965,8 +992,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -981,7 +1008,7 @@
         <v>11001</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -989,8 +1016,67 @@
         <v>22003</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>11601</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>11602</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>21601</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:2">
+      <c r="A7" s="2">
+        <v>11203</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>22202</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>22203</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>22204</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -965,8 +965,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -989,6 +989,22 @@
         <v>22003</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>21006</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>22001</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
     </row>

--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -200,18 +200,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -544,7 +538,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -568,16 +562,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -586,89 +580,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -676,9 +670,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -992,7 +983,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1008,7 +999,7 @@
         <v>11001</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1024,7 +1015,7 @@
         <v>11601</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1032,7 +1023,7 @@
         <v>11602</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1040,11 +1031,11 @@
         <v>21601</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>11203</v>
       </c>
       <c r="B7" s="1">
@@ -1071,12 +1062,41 @@
       <c r="A10">
         <v>22204</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>22008</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>18888</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
     <row r="13" spans="1:2">
-      <c r="B13" s="3"/>
+      <c r="A13">
+        <v>22004</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>22001</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -200,18 +200,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -544,7 +538,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -568,16 +562,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -586,89 +580,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -676,9 +670,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1044,7 +1035,7 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>11203</v>
       </c>
       <c r="B7" s="1">
@@ -1071,12 +1062,12 @@
       <c r="A10">
         <v>22204</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="B13" s="3"/>
+      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1015,7 +1015,7 @@
         <v>11601</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>11602</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/initialHand.xlsx
+++ b/initialHand.xlsx
@@ -1015,7 +1015,7 @@
         <v>11601</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>11602</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2">
